--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_390_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_390_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>6</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -824,10 +824,10 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M3" t="n">
         <v>12</v>
@@ -909,12 +909,12 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1338,7 +1338,7 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>38:38</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AN17" t="n">
@@ -1451,22 +1451,22 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>13.2%</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AN18" t="n">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
@@ -1727,16 +1727,16 @@
         <v>30</v>
       </c>
       <c r="T19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>1</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>45:29</t>
+          <t>25:28</t>
         </is>
       </c>
       <c r="AN19" t="n">
@@ -1843,22 +1843,22 @@
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>37.9%</t>
         </is>
       </c>
     </row>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>41:25</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="AN20" t="n">
@@ -2039,22 +2039,22 @@
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>5.3%</t>
         </is>
       </c>
     </row>
@@ -2125,10 +2125,10 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>02:29</t>
         </is>
       </c>
       <c r="AN21" t="n">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -2315,7 +2315,7 @@
         <v>13</v>
       </c>
       <c r="T22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>41:49</t>
+          <t>21:48</t>
         </is>
       </c>
       <c r="AN22" t="n">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>23.2%</t>
         </is>
       </c>
     </row>
@@ -2511,16 +2511,16 @@
         <v>15</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>5</v>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>36:08</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AN23" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>34.2%</t>
         </is>
       </c>
     </row>
@@ -2707,7 +2707,7 @@
         <v>7</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>38:14</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AN24" t="n">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>13.6%</t>
         </is>
       </c>
     </row>
@@ -2903,10 +2903,10 @@
         <v>22</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>41:05</t>
+          <t>21:04</t>
         </is>
       </c>
       <c r="AN25" t="n">
@@ -3019,22 +3019,22 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>13.8%</t>
         </is>
       </c>
     </row>
@@ -3167,7 +3167,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>05:45</t>
         </is>
       </c>
       <c r="AN26" t="n">
@@ -3215,12 +3215,12 @@
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>19.3%</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3295,16 +3295,16 @@
         <v>12</v>
       </c>
       <c r="T27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
         <v>3</v>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>43:22</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="AN27" t="n">
@@ -3411,22 +3411,22 @@
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>5.3%</t>
         </is>
       </c>
     </row>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>36:28</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AN28" t="n">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3827,16 +3827,16 @@
         <v>129</v>
       </c>
       <c r="T30" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
         <v>16</v>
@@ -4494,10 +4494,10 @@
         <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
         <v>1</v>
@@ -4556,7 +4556,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>49:19</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="AN36" t="n">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>35.2%</t>
         </is>
       </c>
     </row>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>48:33</t>
+          <t>28:31</t>
         </is>
       </c>
       <c r="AN37" t="n">
@@ -4800,22 +4800,22 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>6.4%</t>
         </is>
       </c>
     </row>
@@ -4883,7 +4883,7 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>69:16</t>
+          <t>29:14</t>
         </is>
       </c>
       <c r="AN38" t="n">
@@ -4996,22 +4996,22 @@
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>26.7%</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>07:58</t>
         </is>
       </c>
       <c r="AN39" t="n">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
@@ -5275,7 +5275,7 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>43:15</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AN40" t="n">
@@ -5388,17 +5388,17 @@
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>04:47</t>
+          <t>04:46</t>
         </is>
       </c>
       <c r="AN41" t="n">
@@ -5584,12 +5584,12 @@
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5732,7 +5732,7 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>32:18</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AN42" t="n">
@@ -5780,7 +5780,7 @@
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>32:19</t>
+          <t>22:19</t>
         </is>
       </c>
       <c r="AN43" t="n">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
@@ -5986,12 +5986,12 @@
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>32.0%</t>
         </is>
       </c>
     </row>
@@ -6124,7 +6124,7 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>50:15</t>
+          <t>30:14</t>
         </is>
       </c>
       <c r="AN44" t="n">
@@ -6172,17 +6172,17 @@
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
@@ -6258,10 +6258,10 @@
         <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
         <v>6</v>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>47:27</t>
+          <t>27:26</t>
         </is>
       </c>
       <c r="AN45" t="n">
@@ -6368,17 +6368,17 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
@@ -6451,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>04:47</t>
+          <t>04:46</t>
         </is>
       </c>
       <c r="AN46" t="n">
@@ -6564,22 +6564,22 @@
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>32.3%</t>
         </is>
       </c>
     </row>
@@ -6787,13 +6787,13 @@
         <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="W48" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="X48" t="n">
         <v>17</v>

--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_390_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_390_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M2" t="n">
         <v>6</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -824,10 +824,10 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="M3" t="n">
         <v>12</v>
@@ -909,12 +909,12 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1338,7 +1338,7 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1727,16 +1727,16 @@
         <v>30</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
         <v>1</v>
@@ -2125,10 +2125,10 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2315,7 +2315,7 @@
         <v>13</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -2511,16 +2511,16 @@
         <v>15</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X23" t="n">
         <v>5</v>
@@ -2707,7 +2707,7 @@
         <v>7</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -2903,10 +2903,10 @@
         <v>22</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -3295,16 +3295,16 @@
         <v>12</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X27" t="n">
         <v>3</v>
@@ -3827,16 +3827,16 @@
         <v>129</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X30" t="n">
         <v>16</v>
@@ -4494,10 +4494,10 @@
         <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X36" t="n">
         <v>1</v>
@@ -4883,7 +4883,7 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -5275,7 +5275,7 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -6255,13 +6255,13 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X45" t="n">
         <v>6</v>
@@ -6451,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -6787,13 +6787,13 @@
         <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="V48" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="W48" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="X48" t="n">
         <v>17</v>

--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_390_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_390_EL.xlsx
@@ -674,10 +674,10 @@
         <v>6</v>
       </c>
       <c r="N2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="O2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="P2" t="n">
         <v>19</v>
@@ -833,10 +833,10 @@
         <v>12</v>
       </c>
       <c r="N3" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="P3" t="n">
         <v>17</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>89.47</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1739,14 +1739,14 @@
         <v>1</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA19" t="n">
@@ -2523,10 +2523,10 @@
         <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -2915,10 +2915,10 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
@@ -3111,14 +3111,14 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA26" t="n">
@@ -3307,10 +3307,10 @@
         <v>2</v>
       </c>
       <c r="X27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
@@ -3839,10 +3839,10 @@
         <v>6</v>
       </c>
       <c r="X30" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="Y30" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
@@ -4500,14 +4500,14 @@
         <v>1</v>
       </c>
       <c r="X36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA36" t="n">
@@ -4696,14 +4696,14 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA37" t="n">
@@ -4892,14 +4892,14 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA38" t="n">
@@ -5284,14 +5284,14 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA40" t="n">
@@ -5480,14 +5480,14 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA41" t="n">
@@ -6264,10 +6264,10 @@
         <v>2</v>
       </c>
       <c r="X45" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y45" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
@@ -6460,14 +6460,14 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA46" t="n">
@@ -6796,14 +6796,14 @@
         <v>4</v>
       </c>
       <c r="X48" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="Y48" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA48" t="n">
